--- a/Data/Checklist/Dialogue.xlsx
+++ b/Data/Checklist/Dialogue.xlsx
@@ -1264,7 +1264,7 @@
     <x:col min="7" max="7" width="101.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:7">
+    <x:row r="1" spans="1:7" ht="7" customHeight="1">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -1287,7 +1287,7 @@
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:7">
+    <x:row r="2" spans="1:7" ht="7" customHeight="1">
       <x:c r="A2" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
@@ -1310,7 +1310,7 @@
         <x:v>13</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:7">
+    <x:row r="3" spans="1:7" ht="7" customHeight="1">
       <x:c r="A3" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
@@ -1333,7 +1333,7 @@
         <x:v>19</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:7">
+    <x:row r="4" spans="1:7" ht="7" customHeight="1">
       <x:c r="A4" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
@@ -1356,7 +1356,7 @@
         <x:v>25</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:7">
+    <x:row r="5" spans="1:7" ht="7" customHeight="1">
       <x:c r="A5" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
@@ -1379,7 +1379,7 @@
         <x:v>31</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:7">
+    <x:row r="6" spans="1:7" ht="7" customHeight="1">
       <x:c r="A6" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
@@ -1402,7 +1402,7 @@
         <x:v>37</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" spans="1:7">
+    <x:row r="7" spans="1:7" ht="7" customHeight="1">
       <x:c r="A7" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
@@ -1425,7 +1425,7 @@
         <x:v>43</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" spans="1:7">
+    <x:row r="8" spans="1:7" ht="7" customHeight="1">
       <x:c r="A8" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
@@ -1448,7 +1448,7 @@
         <x:v>49</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:7">
+    <x:row r="9" spans="1:7" ht="7" customHeight="1">
       <x:c r="A9" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
@@ -1471,7 +1471,7 @@
         <x:v>55</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:7">
+    <x:row r="10" spans="1:7" ht="7" customHeight="1">
       <x:c r="A10" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
@@ -1494,7 +1494,7 @@
         <x:v>61</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:7">
+    <x:row r="11" spans="1:7" ht="7" customHeight="1">
       <x:c r="A11" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
@@ -1517,7 +1517,7 @@
         <x:v>67</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:7">
+    <x:row r="12" spans="1:7" ht="7" customHeight="1">
       <x:c r="A12" s="0" t="s">
         <x:v>68</x:v>
       </x:c>
@@ -1540,7 +1540,7 @@
         <x:v>73</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:7">
+    <x:row r="13" spans="1:7" ht="7" customHeight="1">
       <x:c r="A13" s="0" t="s">
         <x:v>74</x:v>
       </x:c>
@@ -1563,7 +1563,7 @@
         <x:v>79</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:7">
+    <x:row r="14" spans="1:7" ht="7" customHeight="1">
       <x:c r="A14" s="0" t="s">
         <x:v>80</x:v>
       </x:c>
@@ -1586,7 +1586,7 @@
         <x:v>85</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:7">
+    <x:row r="15" spans="1:7" ht="7" customHeight="1">
       <x:c r="A15" s="0" t="s">
         <x:v>86</x:v>
       </x:c>
@@ -1609,7 +1609,7 @@
         <x:v>91</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:7">
+    <x:row r="16" spans="1:7" ht="7" customHeight="1">
       <x:c r="A16" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
@@ -1632,7 +1632,7 @@
         <x:v>97</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:7">
+    <x:row r="17" spans="1:7" ht="7" customHeight="1">
       <x:c r="A17" s="0" t="s">
         <x:v>98</x:v>
       </x:c>
@@ -1655,7 +1655,7 @@
         <x:v>103</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:7">
+    <x:row r="18" spans="1:7" ht="7" customHeight="1">
       <x:c r="A18" s="0" t="s">
         <x:v>104</x:v>
       </x:c>
@@ -1678,7 +1678,7 @@
         <x:v>109</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:7">
+    <x:row r="19" spans="1:7" ht="7" customHeight="1">
       <x:c r="A19" s="0" t="s">
         <x:v>110</x:v>
       </x:c>
@@ -1701,7 +1701,7 @@
         <x:v>115</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:7">
+    <x:row r="20" spans="1:7" ht="7" customHeight="1">
       <x:c r="A20" s="0" t="s">
         <x:v>116</x:v>
       </x:c>
@@ -1724,7 +1724,7 @@
         <x:v>121</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:7">
+    <x:row r="21" spans="1:7" ht="7" customHeight="1">
       <x:c r="A21" s="0" t="s">
         <x:v>122</x:v>
       </x:c>
@@ -1747,7 +1747,7 @@
         <x:v>127</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:7">
+    <x:row r="22" spans="1:7" ht="7" customHeight="1">
       <x:c r="A22" s="0" t="s">
         <x:v>128</x:v>
       </x:c>
@@ -1770,7 +1770,7 @@
         <x:v>133</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:7">
+    <x:row r="23" spans="1:7" ht="7" customHeight="1">
       <x:c r="A23" s="0" t="s">
         <x:v>134</x:v>
       </x:c>
@@ -1793,7 +1793,7 @@
         <x:v>139</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:7">
+    <x:row r="24" spans="1:7" ht="7" customHeight="1">
       <x:c r="A24" s="0" t="s">
         <x:v>140</x:v>
       </x:c>
@@ -1816,7 +1816,7 @@
         <x:v>145</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:7">
+    <x:row r="25" spans="1:7" ht="7" customHeight="1">
       <x:c r="A25" s="0" t="s">
         <x:v>146</x:v>
       </x:c>
@@ -1839,7 +1839,7 @@
         <x:v>151</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:7">
+    <x:row r="26" spans="1:7" ht="7" customHeight="1">
       <x:c r="A26" s="0" t="s">
         <x:v>152</x:v>
       </x:c>
@@ -1862,7 +1862,7 @@
         <x:v>157</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:7">
+    <x:row r="27" spans="1:7" ht="7" customHeight="1">
       <x:c r="A27" s="0" t="s">
         <x:v>158</x:v>
       </x:c>
@@ -1885,7 +1885,7 @@
         <x:v>163</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" spans="1:7">
+    <x:row r="28" spans="1:7" ht="7" customHeight="1">
       <x:c r="A28" s="0" t="s">
         <x:v>164</x:v>
       </x:c>
@@ -1908,7 +1908,7 @@
         <x:v>169</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" spans="1:7">
+    <x:row r="29" spans="1:7" ht="7" customHeight="1">
       <x:c r="A29" s="0" t="s">
         <x:v>170</x:v>
       </x:c>
@@ -1931,7 +1931,7 @@
         <x:v>175</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" spans="1:7">
+    <x:row r="30" spans="1:7" ht="7" customHeight="1">
       <x:c r="A30" s="0" t="s">
         <x:v>176</x:v>
       </x:c>
@@ -1954,7 +1954,7 @@
         <x:v>181</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" spans="1:7">
+    <x:row r="31" spans="1:7" ht="7" customHeight="1">
       <x:c r="A31" s="0" t="s">
         <x:v>182</x:v>
       </x:c>
@@ -1977,7 +1977,7 @@
         <x:v>187</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" spans="1:7">
+    <x:row r="32" spans="1:7" ht="7" customHeight="1">
       <x:c r="A32" s="0" t="s">
         <x:v>188</x:v>
       </x:c>
@@ -2000,7 +2000,7 @@
         <x:v>193</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" spans="1:7">
+    <x:row r="33" spans="1:7" ht="7" customHeight="1">
       <x:c r="A33" s="0" t="s">
         <x:v>194</x:v>
       </x:c>
@@ -2023,7 +2023,7 @@
         <x:v>199</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" spans="1:7">
+    <x:row r="34" spans="1:7" ht="7" customHeight="1">
       <x:c r="A34" s="0" t="s">
         <x:v>200</x:v>
       </x:c>
@@ -2046,7 +2046,7 @@
         <x:v>205</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" spans="1:7">
+    <x:row r="35" spans="1:7" ht="7" customHeight="1">
       <x:c r="A35" s="0" t="s">
         <x:v>206</x:v>
       </x:c>
@@ -2069,7 +2069,7 @@
         <x:v>211</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" spans="1:7">
+    <x:row r="36" spans="1:7" ht="7" customHeight="1">
       <x:c r="A36" s="0" t="s">
         <x:v>212</x:v>
       </x:c>
@@ -2092,7 +2092,7 @@
         <x:v>217</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" spans="1:7">
+    <x:row r="37" spans="1:7" ht="7" customHeight="1">
       <x:c r="A37" s="0" t="s">
         <x:v>218</x:v>
       </x:c>
@@ -2115,7 +2115,7 @@
         <x:v>223</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" spans="1:7">
+    <x:row r="38" spans="1:7" ht="7" customHeight="1">
       <x:c r="A38" s="0" t="s">
         <x:v>224</x:v>
       </x:c>
@@ -2138,7 +2138,7 @@
         <x:v>229</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" spans="1:7">
+    <x:row r="39" spans="1:7" ht="7" customHeight="1">
       <x:c r="A39" s="0" t="s">
         <x:v>230</x:v>
       </x:c>
@@ -2161,7 +2161,7 @@
         <x:v>235</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" spans="1:7">
+    <x:row r="40" spans="1:7" ht="7" customHeight="1">
       <x:c r="A40" s="0" t="s">
         <x:v>236</x:v>
       </x:c>
@@ -2184,7 +2184,7 @@
         <x:v>241</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" spans="1:7">
+    <x:row r="41" spans="1:7" ht="7" customHeight="1">
       <x:c r="A41" s="0" t="s">
         <x:v>242</x:v>
       </x:c>
@@ -2207,7 +2207,7 @@
         <x:v>247</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" spans="1:7">
+    <x:row r="42" spans="1:7" ht="7" customHeight="1">
       <x:c r="A42" s="0" t="s">
         <x:v>248</x:v>
       </x:c>
@@ -2230,7 +2230,7 @@
         <x:v>253</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" spans="1:7">
+    <x:row r="43" spans="1:7" ht="7" customHeight="1">
       <x:c r="A43" s="0" t="s">
         <x:v>254</x:v>
       </x:c>
@@ -2253,7 +2253,7 @@
         <x:v>259</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" spans="1:7">
+    <x:row r="44" spans="1:7" ht="7" customHeight="1">
       <x:c r="A44" s="0" t="s">
         <x:v>260</x:v>
       </x:c>
@@ -2276,7 +2276,7 @@
         <x:v>265</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" spans="1:7">
+    <x:row r="45" spans="1:7" ht="7" customHeight="1">
       <x:c r="A45" s="0" t="s">
         <x:v>266</x:v>
       </x:c>
@@ -2299,7 +2299,7 @@
         <x:v>271</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" spans="1:7">
+    <x:row r="46" spans="1:7" ht="7" customHeight="1">
       <x:c r="A46" s="0" t="s">
         <x:v>272</x:v>
       </x:c>
@@ -2322,7 +2322,7 @@
         <x:v>277</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" spans="1:7">
+    <x:row r="47" spans="1:7" ht="7" customHeight="1">
       <x:c r="A47" s="0" t="s">
         <x:v>278</x:v>
       </x:c>
@@ -2345,7 +2345,7 @@
         <x:v>283</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" spans="1:7">
+    <x:row r="48" spans="1:7" ht="7" customHeight="1">
       <x:c r="A48" s="0" t="s">
         <x:v>284</x:v>
       </x:c>
@@ -2368,7 +2368,7 @@
         <x:v>289</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" spans="1:7">
+    <x:row r="49" spans="1:7" ht="7" customHeight="1">
       <x:c r="A49" s="0" t="s">
         <x:v>290</x:v>
       </x:c>
